--- a/docs/DD_北海道3町_20261016/DD結果_筆別一覧_北海道3町.xlsx
+++ b/docs/DD_北海道3町_20261016/DD結果_筆別一覧_北海道3町.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="筆別DD一覧" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'筆別DD一覧'!$A$1:$W$46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'筆別DD一覧'!$A$1:$X$46</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -583,7 +583,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>札前12筆が農用地区域内／No.8が急傾斜 特別警戒区域に接触／道立自然公園 特別地域まで14m〜</t>
+          <t>札前12筆が農用地区域内／No.8の端が急傾斜 特別警戒区域／No.9・11は液状化しやすい地形／道立自然公園 特別地域まで14m〜</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -874,7 +874,7 @@
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>※reinfolib APIキーが無いため、液状化・大規模盛土・用途地域の詳細判定は未実施（都市計画区域外のため用途地域は無し）。垂直積雪量・埋蔵文化財・景観・騒音振動はリンク確認のまま。</t>
+          <t>※不動産情報ライブラリ（2026-10-19取得）で都市計画・洪水・高潮・津波・土砂災害・液状化・自然公園・大規模盛土・地すべり/急傾斜崩壊危険区域を判定済み（大規模盛土・地すべり防止区域・急傾斜地崩壊危険区域は全筆該当なし）。垂直積雪量・埋蔵文化財・景観・騒音振動はリンク確認のまま。</t>
         </is>
       </c>
     </row>
@@ -889,7 +889,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W46"/>
+  <dimension ref="A1:X46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -910,11 +910,12 @@
     <col width="7" customWidth="1" min="16" max="16"/>
     <col width="14" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
-    <col width="22" customWidth="1" min="19" max="19"/>
-    <col width="10" customWidth="1" min="20" max="20"/>
-    <col width="46" customWidth="1" min="21" max="21"/>
-    <col width="8" customWidth="1" min="22" max="22"/>
+    <col width="18" customWidth="1" min="19" max="19"/>
+    <col width="22" customWidth="1" min="20" max="20"/>
+    <col width="10" customWidth="1" min="21" max="21"/>
+    <col width="46" customWidth="1" min="22" max="22"/>
     <col width="8" customWidth="1" min="23" max="23"/>
+    <col width="8" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1010,25 +1011,30 @@
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
+          <t>液状化(地形)</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
           <t>最寄り変電所(距離)</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>判定</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>主な理由</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Googleマップ</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>地理院 航空写真</t>
         </is>
@@ -1117,25 +1123,30 @@
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
+          <t>液状化しにくい（砂礫質台地・傾向5/6）</t>
+        </is>
+      </c>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
           <t>松前変電所(6.7km・座標推定)</t>
         </is>
       </c>
-      <c r="T2" s="4" t="inlineStr">
+      <c r="U2" s="4" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="U2" s="2" t="inlineStr">
+      <c r="V2" s="2" t="inlineStr">
         <is>
           <t>農用地区域に近接13m</t>
         </is>
       </c>
-      <c r="V2" s="7" t="inlineStr">
-        <is>
-          <t>開く</t>
-        </is>
-      </c>
       <c r="W2" s="7" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+      <c r="X2" s="7" t="inlineStr">
         <is>
           <t>開く</t>
         </is>
@@ -1224,25 +1235,30 @@
       </c>
       <c r="S3" s="2" t="inlineStr">
         <is>
+          <t>液状化しにくい（砂礫質台地・傾向5/6）</t>
+        </is>
+      </c>
+      <c r="T3" s="2" t="inlineStr">
+        <is>
           <t>松前変電所(6.7km・座標推定)</t>
         </is>
       </c>
-      <c r="T3" s="4" t="inlineStr">
+      <c r="U3" s="4" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="U3" s="2" t="inlineStr">
+      <c r="V3" s="2" t="inlineStr">
         <is>
           <t>農用地区域に近接56m</t>
         </is>
       </c>
-      <c r="V3" s="7" t="inlineStr">
-        <is>
-          <t>開く</t>
-        </is>
-      </c>
       <c r="W3" s="7" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+      <c r="X3" s="7" t="inlineStr">
         <is>
           <t>開く</t>
         </is>
@@ -1331,25 +1347,30 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
+          <t>液状化しにくい（砂礫質台地・傾向5/6）</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
           <t>松前変電所(6.7km・座標推定)</t>
         </is>
       </c>
-      <c r="T4" s="4" t="inlineStr">
+      <c r="U4" s="4" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="U4" s="2" t="inlineStr">
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>自然公園 特別地域に近接87m</t>
         </is>
       </c>
-      <c r="V4" s="7" t="inlineStr">
-        <is>
-          <t>開く</t>
-        </is>
-      </c>
       <c r="W4" s="7" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+      <c r="X4" s="7" t="inlineStr">
         <is>
           <t>開く</t>
         </is>
@@ -1438,25 +1459,30 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
+          <t>液状化しにくい（砂礫質台地・傾向5/6）</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
           <t>松前変電所(6.7km・座標推定)</t>
         </is>
       </c>
-      <c r="T5" s="4" t="inlineStr">
+      <c r="U5" s="4" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="U5" s="2" t="inlineStr">
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>面積543㎡と小さい</t>
         </is>
       </c>
-      <c r="V5" s="7" t="inlineStr">
-        <is>
-          <t>開く</t>
-        </is>
-      </c>
       <c r="W5" s="7" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+      <c r="X5" s="7" t="inlineStr">
         <is>
           <t>開く</t>
         </is>
@@ -1543,25 +1569,30 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
+          <t>やや液状化しやすい（砂州・砂礫州・傾向3/6）</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
           <t>松前変電所(15.3km)</t>
         </is>
       </c>
-      <c r="T6" s="8" t="inlineStr">
+      <c r="U6" s="8" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="U6" s="2" t="inlineStr">
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>地番110-2が公図に存在しない（分筆未反映等）。登記事項・公図の写しで確認</t>
         </is>
       </c>
-      <c r="V6" s="7" t="inlineStr">
-        <is>
-          <t>開く</t>
-        </is>
-      </c>
       <c r="W6" s="7" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+      <c r="X6" s="7" t="inlineStr">
         <is>
           <t>開く</t>
         </is>
@@ -1650,25 +1681,30 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
+          <t>液状化しにくい（砂礫質台地・傾向5/6）</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
           <t>松前変電所(6.7km・座標推定)</t>
         </is>
       </c>
-      <c r="T7" s="3" t="inlineStr">
+      <c r="U7" s="3" t="inlineStr">
         <is>
           <t>リスク高</t>
         </is>
       </c>
-      <c r="U7" s="2" t="inlineStr">
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>農用地区域内→農振除外が必要</t>
         </is>
       </c>
-      <c r="V7" s="7" t="inlineStr">
-        <is>
-          <t>開く</t>
-        </is>
-      </c>
       <c r="W7" s="7" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+      <c r="X7" s="7" t="inlineStr">
         <is>
           <t>開く</t>
         </is>
@@ -1757,25 +1793,30 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
+          <t>液状化しにくい（砂礫質台地・傾向5/6）</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
           <t>松前変電所(6.7km・座標推定)</t>
         </is>
       </c>
-      <c r="T8" s="3" t="inlineStr">
+      <c r="U8" s="3" t="inlineStr">
         <is>
           <t>リスク高</t>
         </is>
       </c>
-      <c r="U8" s="2" t="inlineStr">
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>農用地区域内→農振除外が必要／自然公園 特別地域に近接34m</t>
         </is>
       </c>
-      <c r="V8" s="7" t="inlineStr">
-        <is>
-          <t>開く</t>
-        </is>
-      </c>
       <c r="W8" s="7" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+      <c r="X8" s="7" t="inlineStr">
         <is>
           <t>開く</t>
         </is>
@@ -1859,30 +1900,35 @@
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t>該当(急傾斜警戒・特別警戒)</t>
+          <t>該当(急傾斜 警戒・特別警戒区域 松前札前4／筆の端 約0.3%)</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
+          <t>液状化しにくい（砂礫質台地・傾向5/6）</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
           <t>松前変電所(6.7km・座標推定)</t>
         </is>
       </c>
-      <c r="T9" s="3" t="inlineStr">
+      <c r="U9" s="3" t="inlineStr">
         <is>
           <t>リスク高</t>
         </is>
       </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>農用地区域内→農振除外が必要／自然公園 特別地域に近接14m／急傾斜 特別警戒区域に接触</t>
-        </is>
-      </c>
-      <c r="V9" s="7" t="inlineStr">
-        <is>
-          <t>開く</t>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>農用地区域内→農振除外が必要／自然公園 特別地域に近接14m／筆の端が急傾斜 特別警戒区域</t>
         </is>
       </c>
       <c r="W9" s="7" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+      <c r="X9" s="7" t="inlineStr">
         <is>
           <t>開く</t>
         </is>
@@ -1971,25 +2017,30 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
+          <t>液状化しやすい（三角州・海岸低地・傾向2/6）</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
           <t>松前変電所(6.7km・座標推定)</t>
         </is>
       </c>
-      <c r="T10" s="3" t="inlineStr">
+      <c r="U10" s="3" t="inlineStr">
         <is>
           <t>リスク高</t>
         </is>
       </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>農用地区域内→農振除外が必要／自然公園 特別地域に近接41m／面積838㎡と小さい</t>
-        </is>
-      </c>
-      <c r="V10" s="7" t="inlineStr">
-        <is>
-          <t>開く</t>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>農用地区域内→農振除外が必要／自然公園 特別地域に近接41m／液状化しやすい地形(三角州・海岸低地)／面積838㎡と小さい</t>
         </is>
       </c>
       <c r="W10" s="7" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+      <c r="X10" s="7" t="inlineStr">
         <is>
           <t>開く</t>
         </is>
@@ -2078,25 +2129,30 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
+          <t>液状化しにくい（砂礫質台地・傾向5/6）</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
           <t>松前変電所(6.7km・座標推定)</t>
         </is>
       </c>
-      <c r="T11" s="3" t="inlineStr">
+      <c r="U11" s="3" t="inlineStr">
         <is>
           <t>リスク高</t>
         </is>
       </c>
-      <c r="U11" s="2" t="inlineStr">
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>農用地区域内→農振除外が必要／自然公園 特別地域に近接97m／面積18㎡と小さい／公図面積13㎡と登記が乖離</t>
         </is>
       </c>
-      <c r="V11" s="7" t="inlineStr">
-        <is>
-          <t>開く</t>
-        </is>
-      </c>
       <c r="W11" s="7" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+      <c r="X11" s="7" t="inlineStr">
         <is>
           <t>開く</t>
         </is>
@@ -2185,25 +2241,30 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
+          <t>液状化しやすい（三角州・海岸低地・傾向2/6）</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
           <t>松前変電所(6.7km・座標推定)</t>
         </is>
       </c>
-      <c r="T12" s="3" t="inlineStr">
+      <c r="U12" s="3" t="inlineStr">
         <is>
           <t>リスク高</t>
         </is>
       </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>農用地区域内→農振除外が必要／自然公園 特別地域に近接27m</t>
-        </is>
-      </c>
-      <c r="V12" s="7" t="inlineStr">
-        <is>
-          <t>開く</t>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>農用地区域内→農振除外が必要／自然公園 特別地域に近接27m／液状化しやすい地形(三角州・海岸低地)</t>
         </is>
       </c>
       <c r="W12" s="7" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+      <c r="X12" s="7" t="inlineStr">
         <is>
           <t>開く</t>
         </is>
@@ -2292,25 +2353,30 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
+          <t>液状化しにくい（砂礫質台地・傾向5/6）</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
           <t>松前変電所(6.7km・座標推定)</t>
         </is>
       </c>
-      <c r="T13" s="3" t="inlineStr">
+      <c r="U13" s="3" t="inlineStr">
         <is>
           <t>リスク高</t>
         </is>
       </c>
-      <c r="U13" s="2" t="inlineStr">
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>農用地区域内→農振除外が必要</t>
         </is>
       </c>
-      <c r="V13" s="7" t="inlineStr">
-        <is>
-          <t>開く</t>
-        </is>
-      </c>
       <c r="W13" s="7" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+      <c r="X13" s="7" t="inlineStr">
         <is>
           <t>開く</t>
         </is>
@@ -2399,25 +2465,30 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
+          <t>液状化しにくい（砂礫質台地・傾向5/6）</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
           <t>松前変電所(6.7km・座標推定)</t>
         </is>
       </c>
-      <c r="T14" s="3" t="inlineStr">
+      <c r="U14" s="3" t="inlineStr">
         <is>
           <t>リスク高</t>
         </is>
       </c>
-      <c r="U14" s="2" t="inlineStr">
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>農用地区域内→農振除外が必要</t>
         </is>
       </c>
-      <c r="V14" s="7" t="inlineStr">
-        <is>
-          <t>開く</t>
-        </is>
-      </c>
       <c r="W14" s="7" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+      <c r="X14" s="7" t="inlineStr">
         <is>
           <t>開く</t>
         </is>
@@ -2506,25 +2577,30 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
+          <t>液状化しにくい（砂礫質台地・傾向5/6）</t>
+        </is>
+      </c>
+      <c r="T15" s="2" t="inlineStr">
+        <is>
           <t>松前変電所(6.7km・座標推定)</t>
         </is>
       </c>
-      <c r="T15" s="3" t="inlineStr">
+      <c r="U15" s="3" t="inlineStr">
         <is>
           <t>リスク高</t>
         </is>
       </c>
-      <c r="U15" s="2" t="inlineStr">
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>農用地区域内→農振除外が必要／自然公園 特別地域に近接83m</t>
         </is>
       </c>
-      <c r="V15" s="7" t="inlineStr">
-        <is>
-          <t>開く</t>
-        </is>
-      </c>
       <c r="W15" s="7" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+      <c r="X15" s="7" t="inlineStr">
         <is>
           <t>開く</t>
         </is>
@@ -2613,25 +2689,30 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
+          <t>液状化しにくい（砂礫質台地・傾向5/6）</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
           <t>松前変電所(6.7km・座標推定)</t>
         </is>
       </c>
-      <c r="T16" s="3" t="inlineStr">
+      <c r="U16" s="3" t="inlineStr">
         <is>
           <t>リスク高</t>
         </is>
       </c>
-      <c r="U16" s="2" t="inlineStr">
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>農用地区域内→農振除外が必要／自然公園 特別地域に近接80m</t>
         </is>
       </c>
-      <c r="V16" s="7" t="inlineStr">
-        <is>
-          <t>開く</t>
-        </is>
-      </c>
       <c r="W16" s="7" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+      <c r="X16" s="7" t="inlineStr">
         <is>
           <t>開く</t>
         </is>
@@ -2720,25 +2801,30 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
+          <t>液状化しにくい（砂礫質台地・傾向5/6）</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
           <t>松前変電所(6.7km・座標推定)</t>
         </is>
       </c>
-      <c r="T17" s="3" t="inlineStr">
+      <c r="U17" s="3" t="inlineStr">
         <is>
           <t>リスク高</t>
         </is>
       </c>
-      <c r="U17" s="2" t="inlineStr">
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>農用地区域内→農振除外が必要</t>
         </is>
       </c>
-      <c r="V17" s="7" t="inlineStr">
-        <is>
-          <t>開く</t>
-        </is>
-      </c>
       <c r="W17" s="7" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+      <c r="X17" s="7" t="inlineStr">
         <is>
           <t>開く</t>
         </is>
@@ -2827,25 +2913,30 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
+          <t>液状化しにくい（砂礫質台地・傾向5/6）</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
           <t>松前変電所(6.7km・座標推定)</t>
         </is>
       </c>
-      <c r="T18" s="3" t="inlineStr">
+      <c r="U18" s="3" t="inlineStr">
         <is>
           <t>リスク高</t>
         </is>
       </c>
-      <c r="U18" s="2" t="inlineStr">
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>農用地区域内→農振除外が必要／面積866㎡と小さい</t>
         </is>
       </c>
-      <c r="V18" s="7" t="inlineStr">
-        <is>
-          <t>開く</t>
-        </is>
-      </c>
       <c r="W18" s="7" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+      <c r="X18" s="7" t="inlineStr">
         <is>
           <t>開く</t>
         </is>
@@ -2933,18 +3024,23 @@
           <t>―</t>
         </is>
       </c>
-      <c r="T19" s="8" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="U19" s="8" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="U19" s="2" t="inlineStr">
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>公図の位置が不正確。法務局で地図(公図)写し・地積測量図を取得し現地特定が必要</t>
         </is>
       </c>
-      <c r="V19" s="2" t="inlineStr"/>
       <c r="W19" s="2" t="inlineStr"/>
+      <c r="X19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
@@ -3028,18 +3124,23 @@
           <t>―</t>
         </is>
       </c>
-      <c r="T20" s="8" t="inlineStr">
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="U20" s="8" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="U20" s="2" t="inlineStr">
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>公図の位置が不正確。法務局で地図(公図)写し・地積測量図を取得し現地特定が必要</t>
         </is>
       </c>
-      <c r="V20" s="2" t="inlineStr"/>
       <c r="W20" s="2" t="inlineStr"/>
+      <c r="X20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
@@ -3123,18 +3224,23 @@
           <t>―</t>
         </is>
       </c>
-      <c r="T21" s="8" t="inlineStr">
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="U21" s="8" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="U21" s="2" t="inlineStr">
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>公図の位置が不正確。法務局で地図(公図)写し・地積測量図を取得し現地特定が必要</t>
         </is>
       </c>
-      <c r="V21" s="2" t="inlineStr"/>
       <c r="W21" s="2" t="inlineStr"/>
+      <c r="X21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
@@ -3218,18 +3324,23 @@
           <t>―</t>
         </is>
       </c>
-      <c r="T22" s="8" t="inlineStr">
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="U22" s="8" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="U22" s="2" t="inlineStr">
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>公図の位置が不正確。法務局で地図(公図)写し・地積測量図を取得し現地特定が必要</t>
         </is>
       </c>
-      <c r="V22" s="2" t="inlineStr"/>
       <c r="W22" s="2" t="inlineStr"/>
+      <c r="X22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
@@ -3313,18 +3424,23 @@
           <t>―</t>
         </is>
       </c>
-      <c r="T23" s="8" t="inlineStr">
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="U23" s="8" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="U23" s="2" t="inlineStr">
+      <c r="V23" s="2" t="inlineStr">
         <is>
           <t>公図の位置が不正確。法務局で地図(公図)写し・地積測量図を取得し現地特定が必要</t>
         </is>
       </c>
-      <c r="V23" s="2" t="inlineStr"/>
       <c r="W23" s="2" t="inlineStr"/>
+      <c r="X23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
@@ -3409,25 +3525,30 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
+          <t>液状化しにくい（砂礫質台地・傾向5/6）</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
           <t>松前変電所(13.0km・座標推定)</t>
         </is>
       </c>
-      <c r="T24" s="3" t="inlineStr">
+      <c r="U24" s="3" t="inlineStr">
         <is>
           <t>リスク高</t>
         </is>
       </c>
-      <c r="U24" s="2" t="inlineStr">
+      <c r="V24" s="2" t="inlineStr">
         <is>
           <t>道立自然公園 特別地域内／変電所まで13km</t>
         </is>
       </c>
-      <c r="V24" s="7" t="inlineStr">
-        <is>
-          <t>開く</t>
-        </is>
-      </c>
       <c r="W24" s="7" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+      <c r="X24" s="7" t="inlineStr">
         <is>
           <t>開く</t>
         </is>
@@ -3516,25 +3637,30 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
+          <t>液状化しにくい（砂礫質台地・傾向5/6）</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
           <t>上ノ国変電所(21.7km・座標推定)</t>
         </is>
       </c>
-      <c r="T25" s="4" t="inlineStr">
+      <c r="U25" s="4" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="U25" s="2" t="inlineStr">
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>面積832㎡と小さい／変電所まで22km／公図面積468㎡と登記が乖離</t>
         </is>
       </c>
-      <c r="V25" s="7" t="inlineStr">
-        <is>
-          <t>開く</t>
-        </is>
-      </c>
       <c r="W25" s="7" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+      <c r="X25" s="7" t="inlineStr">
         <is>
           <t>開く</t>
         </is>
@@ -3623,25 +3749,30 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
+          <t>液状化しにくい（砂礫質台地・傾向5/6）</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
           <t>上ノ国変電所(21.7km・座標推定)</t>
         </is>
       </c>
-      <c r="T26" s="4" t="inlineStr">
+      <c r="U26" s="4" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="U26" s="2" t="inlineStr">
+      <c r="V26" s="2" t="inlineStr">
         <is>
           <t>変電所まで22km</t>
         </is>
       </c>
-      <c r="V26" s="7" t="inlineStr">
-        <is>
-          <t>開く</t>
-        </is>
-      </c>
       <c r="W26" s="7" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+      <c r="X26" s="7" t="inlineStr">
         <is>
           <t>開く</t>
         </is>
@@ -3730,25 +3861,30 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
+          <t>液状化しにくい（砂礫質台地・傾向5/6）</t>
+        </is>
+      </c>
+      <c r="T27" s="2" t="inlineStr">
+        <is>
           <t>上ノ国変電所(21.7km・座標推定)</t>
         </is>
       </c>
-      <c r="T27" s="4" t="inlineStr">
+      <c r="U27" s="4" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="U27" s="2" t="inlineStr">
+      <c r="V27" s="2" t="inlineStr">
         <is>
           <t>変電所まで22km</t>
         </is>
       </c>
-      <c r="V27" s="7" t="inlineStr">
-        <is>
-          <t>開く</t>
-        </is>
-      </c>
       <c r="W27" s="7" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+      <c r="X27" s="7" t="inlineStr">
         <is>
           <t>開く</t>
         </is>
@@ -3837,25 +3973,30 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
+          <t>液状化しにくい（砂礫質台地・傾向5/6）</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
           <t>上ノ国変電所(21.7km・座標推定)</t>
         </is>
       </c>
-      <c r="T28" s="4" t="inlineStr">
+      <c r="U28" s="4" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="U28" s="2" t="inlineStr">
+      <c r="V28" s="2" t="inlineStr">
         <is>
           <t>変電所まで22km</t>
         </is>
       </c>
-      <c r="V28" s="7" t="inlineStr">
-        <is>
-          <t>開く</t>
-        </is>
-      </c>
       <c r="W28" s="7" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+      <c r="X28" s="7" t="inlineStr">
         <is>
           <t>開く</t>
         </is>
@@ -3944,25 +4085,30 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
+          <t>液状化しにくい（砂礫質台地・傾向5/6）</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
           <t>上ノ国変電所(21.7km・座標推定)</t>
         </is>
       </c>
-      <c r="T29" s="4" t="inlineStr">
+      <c r="U29" s="4" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="U29" s="2" t="inlineStr">
+      <c r="V29" s="2" t="inlineStr">
         <is>
           <t>面積770㎡と小さい／変電所まで22km</t>
         </is>
       </c>
-      <c r="V29" s="7" t="inlineStr">
-        <is>
-          <t>開く</t>
-        </is>
-      </c>
       <c r="W29" s="7" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+      <c r="X29" s="7" t="inlineStr">
         <is>
           <t>開く</t>
         </is>
@@ -4051,25 +4197,30 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
+          <t>液状化しにくい（砂礫質台地・傾向5/6）</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
           <t>上ノ国変電所(21.7km・座標推定)</t>
         </is>
       </c>
-      <c r="T30" s="4" t="inlineStr">
+      <c r="U30" s="4" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="U30" s="2" t="inlineStr">
+      <c r="V30" s="2" t="inlineStr">
         <is>
           <t>変電所まで22km</t>
         </is>
       </c>
-      <c r="V30" s="7" t="inlineStr">
-        <is>
-          <t>開く</t>
-        </is>
-      </c>
       <c r="W30" s="7" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+      <c r="X30" s="7" t="inlineStr">
         <is>
           <t>開く</t>
         </is>
@@ -4158,25 +4309,30 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
+          <t>液状化しにくい（砂礫質台地・傾向5/6）</t>
+        </is>
+      </c>
+      <c r="T31" s="2" t="inlineStr">
+        <is>
           <t>上ノ国変電所(21.7km・座標推定)</t>
         </is>
       </c>
-      <c r="T31" s="4" t="inlineStr">
+      <c r="U31" s="4" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="U31" s="2" t="inlineStr">
+      <c r="V31" s="2" t="inlineStr">
         <is>
           <t>面積960㎡と小さい／変電所まで22km／公図面積807㎡と登記が乖離</t>
         </is>
       </c>
-      <c r="V31" s="7" t="inlineStr">
-        <is>
-          <t>開く</t>
-        </is>
-      </c>
       <c r="W31" s="7" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+      <c r="X31" s="7" t="inlineStr">
         <is>
           <t>開く</t>
         </is>
@@ -4265,25 +4421,30 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
+          <t>液状化しにくい（砂礫質台地・傾向5/6）</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
           <t>上ノ国変電所(1.1km・座標推定)</t>
         </is>
       </c>
-      <c r="T32" s="3" t="inlineStr">
+      <c r="U32" s="3" t="inlineStr">
         <is>
           <t>リスク高</t>
         </is>
       </c>
-      <c r="U32" s="2" t="inlineStr">
+      <c r="V32" s="2" t="inlineStr">
         <is>
           <t>農用地区域内→農振除外が必要／津波浸水想定 0.3m未満/0.5〜1m/1〜3m</t>
         </is>
       </c>
-      <c r="V32" s="7" t="inlineStr">
-        <is>
-          <t>開く</t>
-        </is>
-      </c>
       <c r="W32" s="7" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+      <c r="X32" s="7" t="inlineStr">
         <is>
           <t>開く</t>
         </is>
@@ -4372,25 +4533,30 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
+          <t>液状化しにくい（砂礫質台地・傾向5/6）</t>
+        </is>
+      </c>
+      <c r="T33" s="2" t="inlineStr">
+        <is>
           <t>上ノ国変電所(1.1km・座標推定)</t>
         </is>
       </c>
-      <c r="T33" s="3" t="inlineStr">
+      <c r="U33" s="3" t="inlineStr">
         <is>
           <t>リスク高</t>
         </is>
       </c>
-      <c r="U33" s="2" t="inlineStr">
+      <c r="V33" s="2" t="inlineStr">
         <is>
           <t>農用地区域内→農振除外が必要</t>
         </is>
       </c>
-      <c r="V33" s="7" t="inlineStr">
-        <is>
-          <t>開く</t>
-        </is>
-      </c>
       <c r="W33" s="7" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+      <c r="X33" s="7" t="inlineStr">
         <is>
           <t>開く</t>
         </is>
@@ -4479,25 +4645,30 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
+          <t>液状化しにくい（砂礫質台地・傾向5/6）</t>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
           <t>上ノ国変電所(1.1km・座標推定)</t>
         </is>
       </c>
-      <c r="T34" s="3" t="inlineStr">
+      <c r="U34" s="3" t="inlineStr">
         <is>
           <t>リスク高</t>
         </is>
       </c>
-      <c r="U34" s="2" t="inlineStr">
+      <c r="V34" s="2" t="inlineStr">
         <is>
           <t>農用地区域内→農振除外が必要</t>
         </is>
       </c>
-      <c r="V34" s="7" t="inlineStr">
-        <is>
-          <t>開く</t>
-        </is>
-      </c>
       <c r="W34" s="7" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+      <c r="X34" s="7" t="inlineStr">
         <is>
           <t>開く</t>
         </is>
@@ -4586,25 +4757,30 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
+          <t>液状化しにくい（砂礫質台地・傾向5/6）</t>
+        </is>
+      </c>
+      <c r="T35" s="2" t="inlineStr">
+        <is>
           <t>上ノ国変電所(1.1km・座標推定)</t>
         </is>
       </c>
-      <c r="T35" s="3" t="inlineStr">
+      <c r="U35" s="3" t="inlineStr">
         <is>
           <t>リスク高</t>
         </is>
       </c>
-      <c r="U35" s="2" t="inlineStr">
+      <c r="V35" s="2" t="inlineStr">
         <is>
           <t>農用地区域内→農振除外が必要</t>
         </is>
       </c>
-      <c r="V35" s="7" t="inlineStr">
-        <is>
-          <t>開く</t>
-        </is>
-      </c>
       <c r="W35" s="7" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+      <c r="X35" s="7" t="inlineStr">
         <is>
           <t>開く</t>
         </is>
@@ -4693,25 +4869,30 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
+          <t>液状化しにくい（砂礫質台地・傾向5/6）</t>
+        </is>
+      </c>
+      <c r="T36" s="2" t="inlineStr">
+        <is>
           <t>上ノ国変電所(1.1km・座標推定)</t>
         </is>
       </c>
-      <c r="T36" s="3" t="inlineStr">
+      <c r="U36" s="3" t="inlineStr">
         <is>
           <t>リスク高</t>
         </is>
       </c>
-      <c r="U36" s="2" t="inlineStr">
+      <c r="V36" s="2" t="inlineStr">
         <is>
           <t>農用地区域内→農振除外が必要</t>
         </is>
       </c>
-      <c r="V36" s="7" t="inlineStr">
-        <is>
-          <t>開く</t>
-        </is>
-      </c>
       <c r="W36" s="7" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+      <c r="X36" s="7" t="inlineStr">
         <is>
           <t>開く</t>
         </is>
@@ -4800,25 +4981,30 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
+          <t>液状化しにくい（砂礫質台地・傾向5/6）</t>
+        </is>
+      </c>
+      <c r="T37" s="2" t="inlineStr">
+        <is>
           <t>上ノ国変電所(1.1km・座標推定)</t>
         </is>
       </c>
-      <c r="T37" s="3" t="inlineStr">
+      <c r="U37" s="3" t="inlineStr">
         <is>
           <t>リスク高</t>
         </is>
       </c>
-      <c r="U37" s="2" t="inlineStr">
+      <c r="V37" s="2" t="inlineStr">
         <is>
           <t>農用地区域内→農振除外が必要</t>
         </is>
       </c>
-      <c r="V37" s="7" t="inlineStr">
-        <is>
-          <t>開く</t>
-        </is>
-      </c>
       <c r="W37" s="7" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+      <c r="X37" s="7" t="inlineStr">
         <is>
           <t>開く</t>
         </is>
@@ -4907,25 +5093,30 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
+          <t>液状化しにくい（砂礫質台地・傾向5/6）</t>
+        </is>
+      </c>
+      <c r="T38" s="2" t="inlineStr">
+        <is>
           <t>上ノ国変電所(1.1km・座標推定)</t>
         </is>
       </c>
-      <c r="T38" s="3" t="inlineStr">
+      <c r="U38" s="3" t="inlineStr">
         <is>
           <t>リスク高</t>
         </is>
       </c>
-      <c r="U38" s="2" t="inlineStr">
+      <c r="V38" s="2" t="inlineStr">
         <is>
           <t>農用地区域内→農振除外が必要</t>
         </is>
       </c>
-      <c r="V38" s="7" t="inlineStr">
-        <is>
-          <t>開く</t>
-        </is>
-      </c>
       <c r="W38" s="7" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+      <c r="X38" s="7" t="inlineStr">
         <is>
           <t>開く</t>
         </is>
@@ -5014,25 +5205,30 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
+          <t>液状化しにくい（砂礫質台地・傾向5/6）</t>
+        </is>
+      </c>
+      <c r="T39" s="2" t="inlineStr">
+        <is>
           <t>上ノ国変電所(1.1km・座標推定)</t>
         </is>
       </c>
-      <c r="T39" s="3" t="inlineStr">
+      <c r="U39" s="3" t="inlineStr">
         <is>
           <t>リスク高</t>
         </is>
       </c>
-      <c r="U39" s="2" t="inlineStr">
+      <c r="V39" s="2" t="inlineStr">
         <is>
           <t>農用地区域内→農振除外が必要／津波浸水想定 1〜3m</t>
         </is>
       </c>
-      <c r="V39" s="7" t="inlineStr">
-        <is>
-          <t>開く</t>
-        </is>
-      </c>
       <c r="W39" s="7" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+      <c r="X39" s="7" t="inlineStr">
         <is>
           <t>開く</t>
         </is>
@@ -5121,25 +5317,30 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
+          <t>液状化しにくい（砂礫質台地・傾向5/6）</t>
+        </is>
+      </c>
+      <c r="T40" s="2" t="inlineStr">
+        <is>
           <t>上ノ国変電所(1.1km・座標推定)</t>
         </is>
       </c>
-      <c r="T40" s="3" t="inlineStr">
+      <c r="U40" s="3" t="inlineStr">
         <is>
           <t>リスク高</t>
         </is>
       </c>
-      <c r="U40" s="2" t="inlineStr">
+      <c r="V40" s="2" t="inlineStr">
         <is>
           <t>農用地区域内→農振除外が必要</t>
         </is>
       </c>
-      <c r="V40" s="7" t="inlineStr">
-        <is>
-          <t>開く</t>
-        </is>
-      </c>
       <c r="W40" s="7" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+      <c r="X40" s="7" t="inlineStr">
         <is>
           <t>開く</t>
         </is>
@@ -5228,25 +5429,30 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
+          <t>液状化しにくい（砂礫質台地・傾向5/6）</t>
+        </is>
+      </c>
+      <c r="T41" s="2" t="inlineStr">
+        <is>
           <t>上ノ国変電所(1.1km・座標推定)</t>
         </is>
       </c>
-      <c r="T41" s="3" t="inlineStr">
+      <c r="U41" s="3" t="inlineStr">
         <is>
           <t>リスク高</t>
         </is>
       </c>
-      <c r="U41" s="2" t="inlineStr">
+      <c r="V41" s="2" t="inlineStr">
         <is>
           <t>農用地区域内→農振除外が必要</t>
         </is>
       </c>
-      <c r="V41" s="7" t="inlineStr">
-        <is>
-          <t>開く</t>
-        </is>
-      </c>
       <c r="W41" s="7" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+      <c r="X41" s="7" t="inlineStr">
         <is>
           <t>開く</t>
         </is>
@@ -5335,25 +5541,30 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
+          <t>液状化しにくい（砂礫質台地・傾向5/6）</t>
+        </is>
+      </c>
+      <c r="T42" s="2" t="inlineStr">
+        <is>
           <t>上ノ国変電所(1.1km・座標推定)</t>
         </is>
       </c>
-      <c r="T42" s="3" t="inlineStr">
+      <c r="U42" s="3" t="inlineStr">
         <is>
           <t>リスク高</t>
         </is>
       </c>
-      <c r="U42" s="2" t="inlineStr">
+      <c r="V42" s="2" t="inlineStr">
         <is>
           <t>農用地区域内→農振除外が必要</t>
         </is>
       </c>
-      <c r="V42" s="7" t="inlineStr">
-        <is>
-          <t>開く</t>
-        </is>
-      </c>
       <c r="W42" s="7" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+      <c r="X42" s="7" t="inlineStr">
         <is>
           <t>開く</t>
         </is>
@@ -5442,25 +5653,30 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
+          <t>液状化しにくい（砂礫質台地・傾向5/6）</t>
+        </is>
+      </c>
+      <c r="T43" s="2" t="inlineStr">
+        <is>
           <t>上ノ国変電所(1.1km・座標推定)</t>
         </is>
       </c>
-      <c r="T43" s="3" t="inlineStr">
+      <c r="U43" s="3" t="inlineStr">
         <is>
           <t>リスク高</t>
         </is>
       </c>
-      <c r="U43" s="2" t="inlineStr">
+      <c r="V43" s="2" t="inlineStr">
         <is>
           <t>農用地区域内→農振除外が必要／面積449㎡と小さい</t>
         </is>
       </c>
-      <c r="V43" s="7" t="inlineStr">
-        <is>
-          <t>開く</t>
-        </is>
-      </c>
       <c r="W43" s="7" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+      <c r="X43" s="7" t="inlineStr">
         <is>
           <t>開く</t>
         </is>
@@ -5549,25 +5765,30 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
+          <t>液状化しにくい（砂礫質台地・傾向5/6）</t>
+        </is>
+      </c>
+      <c r="T44" s="2" t="inlineStr">
+        <is>
           <t>西中川変電所(18.5km・座標推定)</t>
         </is>
       </c>
-      <c r="T44" s="4" t="inlineStr">
+      <c r="U44" s="4" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="U44" s="2" t="inlineStr">
+      <c r="V44" s="2" t="inlineStr">
         <is>
           <t>農用地区域に一部(18%)かかる→境界確認／森林計画民有林内→伐採届/林地開発許可／変電所まで18km</t>
         </is>
       </c>
-      <c r="V44" s="7" t="inlineStr">
-        <is>
-          <t>開く</t>
-        </is>
-      </c>
       <c r="W44" s="7" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+      <c r="X44" s="7" t="inlineStr">
         <is>
           <t>開く</t>
         </is>
@@ -5656,25 +5877,30 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
+          <t>液状化しにくい（砂礫質台地・傾向5/6）</t>
+        </is>
+      </c>
+      <c r="T45" s="2" t="inlineStr">
+        <is>
           <t>西中川変電所(18.5km・座標推定)</t>
         </is>
       </c>
-      <c r="T45" s="4" t="inlineStr">
+      <c r="U45" s="4" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="U45" s="2" t="inlineStr">
+      <c r="V45" s="2" t="inlineStr">
         <is>
           <t>農用地区域に近接0m／森林計画民有林内→伐採届/林地開発許可／変電所まで18km</t>
         </is>
       </c>
-      <c r="V45" s="7" t="inlineStr">
-        <is>
-          <t>開く</t>
-        </is>
-      </c>
       <c r="W45" s="7" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+      <c r="X45" s="7" t="inlineStr">
         <is>
           <t>開く</t>
         </is>
@@ -5763,113 +5989,118 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
+          <t>液状化しにくい（砂礫質台地・傾向5/6）</t>
+        </is>
+      </c>
+      <c r="T46" s="2" t="inlineStr">
+        <is>
           <t>西中川変電所(18.5km・座標推定)</t>
         </is>
       </c>
-      <c r="T46" s="4" t="inlineStr">
+      <c r="U46" s="4" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="U46" s="2" t="inlineStr">
+      <c r="V46" s="2" t="inlineStr">
         <is>
           <t>農用地区域に近接15m／森林計画民有林内→伐採届/林地開発許可／変電所まで18km</t>
         </is>
       </c>
-      <c r="V46" s="7" t="inlineStr">
-        <is>
-          <t>開く</t>
-        </is>
-      </c>
       <c r="W46" s="7" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+      <c r="X46" s="7" t="inlineStr">
         <is>
           <t>開く</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:W46"/>
+  <autoFilter ref="A1:X46"/>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W2" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V3" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W3" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V4" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W4" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V5" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W5" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V6" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W6" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V7" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W7" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V8" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W8" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V9" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W9" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V10" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W10" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V11" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W11" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V12" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W12" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V13" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W13" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V14" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W14" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V15" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W15" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V16" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W16" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V17" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W17" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V18" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W18" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V24" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W24" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V25" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W25" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V26" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W26" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V27" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W27" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V28" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W28" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V29" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W29" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V30" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W30" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V31" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W31" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V32" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W32" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V33" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W33" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V34" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W34" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V35" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W35" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V36" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W36" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V37" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W37" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V38" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W38" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V39" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W39" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V40" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W40" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V41" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W41" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V42" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W42" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V43" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W43" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V44" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W44" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V45" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W45" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V46" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W46" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W3" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W4" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X4" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W5" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X5" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W6" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X6" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W7" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X7" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W8" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X8" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W9" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X9" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W10" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X10" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W11" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X11" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W12" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X12" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W13" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X13" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W14" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X14" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W15" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X15" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W16" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X16" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W17" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X17" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W18" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X18" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W24" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X24" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W25" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X25" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W26" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X26" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W27" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X27" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W28" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X28" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W29" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X29" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W30" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X30" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W31" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X31" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W32" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X32" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W33" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X33" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W34" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X34" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W35" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X35" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W36" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X36" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W37" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X37" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W38" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X38" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W39" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X39" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W40" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X40" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W41" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X41" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W42" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X42" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W43" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X43" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W44" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X44" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W45" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X45" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W46" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X46" r:id="rId80"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
